--- a/UTCUTS/A1_Outputs/previous_version_1/A-O_AR_Model_Base_Year_PREV1.xlsx
+++ b/UTCUTS/A1_Outputs/previous_version_1/A-O_AR_Model_Base_Year_PREV1.xlsx
@@ -6193,7 +6193,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9561A371-ED12-4587-88A7-520B4488FA8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABAD3228-946E-4342-AD9C-C0AC32B8CCDB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
